--- a/Versão5/MOTO/Ontologia_Motriz.xlsx
+++ b/Versão5/MOTO/Ontologia_Motriz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480BACDB-EB73-4517-B3E1-2D4D7064EE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBB5D20-9872-4527-9FD2-131DB9D6C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Interop" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!$C$2:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="198">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -324,16 +324,7 @@
     <t>Contêiner</t>
   </si>
   <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Produzido</t>
-  </si>
-  <si>
     <t>Informação</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informção de acordo à norma NBR 19650-1.</t>
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
@@ -380,9 +371,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard.</t>
-  </si>
-  <si>
     <t>CTI_Projeto_01</t>
   </si>
   <si>
@@ -639,6 +627,45 @@
   </si>
   <si>
     <t>[ 3E.08.06.10.02 ]</t>
+  </si>
+  <si>
+    <t>Definida</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Requerida</t>
+  </si>
+  <si>
+    <t>No.Projeto</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>Requisito.Espacial</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Mobiliário</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Equipamento</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Sistemas</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
 </sst>
 </file>
@@ -746,12 +773,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2AA84"/>
         <bgColor rgb="FFF6C6AD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E896"/>
-        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -868,6 +889,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9F2D0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -981,24 +1008,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1014,10 +1041,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1030,64 +1057,64 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1096,7 +1123,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1111,7 +1138,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1123,16 +1150,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1153,25 +1177,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1180,26 +1204,32 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="32">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1243,6 +1273,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1280,6 +1326,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1456,328 +1510,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2235,7 +1967,7 @@
         <v>46</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2246,7 +1978,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2254,10 +1986,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2268,7 +2000,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2280,7 +2012,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2292,7 +2024,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2303,7 +2035,7 @@
         <v>54</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="44" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2311,10 +2043,10 @@
         <v>55</v>
       </c>
       <c r="B8" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="46" t="s">
         <v>93</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2325,7 +2057,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2336,7 +2068,7 @@
         <v>59</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2347,7 +2079,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2358,7 +2090,7 @@
         <v>59</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2369,7 +2101,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2380,7 +2112,7 @@
         <v>59</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2391,7 +2123,7 @@
         <v>59</v>
       </c>
       <c r="C15" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2402,7 +2134,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2410,10 +2142,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2422,10 +2154,10 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46135.635253819448</v>
+        <v>46139.506402662038</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2436,7 +2168,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2447,7 +2179,7 @@
         <v>59</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2458,7 +2190,7 @@
         <v>59</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2466,10 +2198,10 @@
         <v>72</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C22" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2477,22 +2209,22 @@
         <v>73</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C23" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="44" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Mechanical Driving Systems</v>
       </c>
       <c r="C24" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2503,7 +2235,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.15234375" customWidth="1"/>
@@ -2526,47 +2258,47 @@
     <col min="22" max="22" width="5.69140625" customWidth="1"/>
     <col min="23" max="23" width="7.3828125" customWidth="1"/>
     <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.53515625" style="58" customWidth="1"/>
+    <col min="25" max="25" width="15.53515625" style="57" customWidth="1"/>
     <col min="26" max="26" width="7.921875" style="38" customWidth="1"/>
-    <col min="27" max="27" width="33" customWidth="1"/>
+    <col min="27" max="27" width="40.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="54" t="s">
+      <c r="A1" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="54" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M1" s="41" t="s">
         <v>5</v>
@@ -2583,8 +2315,8 @@
       <c r="Q1" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="56" t="s">
-        <v>101</v>
+      <c r="R1" s="55" t="s">
+        <v>98</v>
       </c>
       <c r="S1" s="41" t="s">
         <v>33</v>
@@ -2592,26 +2324,26 @@
       <c r="T1" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="57" t="s">
+      <c r="U1" s="56" t="s">
         <v>35</v>
       </c>
       <c r="V1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="67" t="s">
+      <c r="W1" s="66" t="s">
         <v>8</v>
       </c>
       <c r="X1" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y1" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z1" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="42" t="s">
         <v>89</v>
-      </c>
-      <c r="Y1" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z1" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" s="42" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2619,78 +2351,77 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="35" t="str">
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="M2" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N2" s="35" t="str">
+        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Definida</v>
+      </c>
+      <c r="O2" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>No Projeto</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="35" t="str">
-        <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="35" t="str">
-        <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
-        <v>Produzido</v>
-      </c>
-      <c r="N2" s="35" t="str">
-        <f t="shared" ref="N2" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+      <c r="R2" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="37" t="str">
+        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="T2" s="37" t="str">
+        <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="O2" s="31" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="37" t="str">
-        <f t="shared" ref="S2" si="3">SUBSTITUTE(C2, "_", " ")</f>
-        <v>Gestão</v>
-      </c>
-      <c r="T2" s="37" t="str">
-        <f t="shared" ref="T2" si="4">SUBSTITUTE(D2, "_", " ")</f>
-        <v>Produzido</v>
-      </c>
       <c r="U2" s="37" t="str">
-        <f t="shared" ref="U2" si="5">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Informação</v>
-      </c>
-      <c r="V2" s="37" t="str">
-        <f t="shared" ref="V2" si="6">SUBSTITUTE(C2, "_", " ")</f>
-        <v>Gestão</v>
+        <f t="shared" si="2"/>
+        <v>Definida</v>
+      </c>
+      <c r="V2" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="W2" s="68" t="str">
-        <f>CONCATENATE("Key-MOT-",A2)</f>
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-MOT-",A2)</f>
         <v>Key-MOT-2</v>
       </c>
       <c r="X2" s="31" t="s">
@@ -2702,8 +2433,9 @@
       <c r="Z2" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="31" t="s">
-        <v>102</v>
+      <c r="AA2" s="31" t="str">
+        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2711,19 +2443,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>120</v>
+        <v>189</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="65" t="s">
-        <v>121</v>
+        <v>187</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>190</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>9</v>
@@ -2741,62 +2473,61 @@
         <v>9</v>
       </c>
       <c r="L3" s="35" t="str">
-        <f t="shared" ref="L3:L5" si="7">CONCATENATE("", C3)</f>
-        <v>Motricidade</v>
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
       </c>
       <c r="M3" s="35" t="str">
-        <f t="shared" ref="M3:M5" si="8">CONCATENATE("", D3)</f>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="0"/>
+        <v>Informação</v>
       </c>
       <c r="N3" s="35" t="str">
-        <f t="shared" ref="N3:N5" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
-        <v>Maquinária</v>
-      </c>
-      <c r="O3" s="31" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F3)),CONCATENATE("Classe IFC:   ",F3),F3)</f>
-        <v>Motor.de.Combustão</v>
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O3" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="31" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="Q3" s="31" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="R3" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="37" t="str">
-        <f t="shared" ref="S3:S16" si="10">SUBSTITUTE(C3, "_", " ")</f>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
       </c>
       <c r="T3" s="37" t="str">
-        <f t="shared" ref="T3:T16" si="11">SUBSTITUTE(D3, "_", " ")</f>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="2"/>
+        <v>Informação</v>
       </c>
       <c r="U3" s="37" t="str">
-        <f t="shared" ref="U3:U16" si="12">SUBSTITUTE(E3, "_", " ")</f>
-        <v>Maquinária</v>
-      </c>
-      <c r="V3" s="37" t="str">
-        <f t="shared" ref="V3:V16" si="13">SUBSTITUTE(C3, "_", " ")</f>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V3" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="W3" s="68" t="str">
-        <f t="shared" ref="W3:W16" si="14">CONCATENATE("Key-MOT-",A3)</f>
+        <f t="shared" si="3"/>
         <v>Key-MOT-3</v>
       </c>
       <c r="X3" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>113</v>
+        <v>9</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="Z3" s="36" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="AA3" s="31" t="str">
-        <f t="shared" ref="AA3:AA5" si="15">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Combustion engine</v>
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2804,19 +2535,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>120</v>
+        <v>189</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>117</v>
+        <v>187</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>192</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>9</v>
@@ -2834,62 +2565,61 @@
         <v>9</v>
       </c>
       <c r="L4" s="35" t="str">
-        <f t="shared" ref="L4" si="16">CONCATENATE("", C4)</f>
-        <v>Motricidade</v>
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
       </c>
       <c r="M4" s="35" t="str">
-        <f t="shared" ref="M4" si="17">CONCATENATE("", D4)</f>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="0"/>
+        <v>Informação</v>
       </c>
       <c r="N4" s="35" t="str">
-        <f t="shared" ref="N4" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
-        <v>Maquinária</v>
-      </c>
-      <c r="O4" s="31" t="str">
-        <f t="shared" ref="O4:O16" si="19">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),F4)</f>
-        <v>Motor.de.Acoplamento</v>
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O4" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="31" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="R4" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="37" t="str">
-        <f t="shared" si="10"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
       </c>
       <c r="T4" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="2"/>
+        <v>Informação</v>
       </c>
       <c r="U4" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V4" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="W4" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="3"/>
         <v>Key-MOT-4</v>
       </c>
       <c r="X4" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>114</v>
+        <v>9</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="Z4" s="36" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="AA4" s="31" t="str">
-        <f t="shared" ref="AA4" si="20">_xlfn.TRANSLATE(P4,"pt","en")</f>
-        <v>Coupling motor</v>
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2897,19 +2627,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>120</v>
+        <v>189</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="65" t="s">
-        <v>119</v>
+        <v>187</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>194</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>9</v>
@@ -2927,62 +2657,61 @@
         <v>9</v>
       </c>
       <c r="L5" s="35" t="str">
-        <f t="shared" si="7"/>
-        <v>Motricidade</v>
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
       </c>
       <c r="M5" s="35" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="0"/>
+        <v>Informação</v>
       </c>
       <c r="N5" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="O5" s="31" t="str">
-        <f t="shared" si="19"/>
-        <v>Motor.de.Acionamento.Correia</v>
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O5" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="31" t="s">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="Q5" s="31" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="R5" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="37" t="str">
-        <f t="shared" si="10"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
       </c>
       <c r="T5" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="2"/>
+        <v>Informação</v>
       </c>
       <c r="U5" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V5" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="W5" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="3"/>
         <v>Key-MOT-5</v>
       </c>
       <c r="X5" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>115</v>
+        <v>9</v>
+      </c>
+      <c r="Y5" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="Z5" s="36" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="AA5" s="31" t="str">
-        <f t="shared" si="15"/>
-        <v>Belt drive motor</v>
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2990,19 +2719,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>120</v>
+        <v>189</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>118</v>
+        <v>187</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>196</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>9</v>
@@ -3020,62 +2749,61 @@
         <v>9</v>
       </c>
       <c r="L6" s="35" t="str">
-        <f t="shared" ref="L6" si="21">CONCATENATE("", C6)</f>
-        <v>Motricidade</v>
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
       </c>
       <c r="M6" s="35" t="str">
-        <f t="shared" ref="M6" si="22">CONCATENATE("", D6)</f>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="0"/>
+        <v>Informação</v>
       </c>
       <c r="N6" s="35" t="str">
-        <f t="shared" ref="N6" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
-        <v>Maquinária</v>
-      </c>
-      <c r="O6" s="31" t="str">
-        <f t="shared" si="19"/>
-        <v>Motor.de.Acionamento.Direto</v>
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O6" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="R6" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="37" t="str">
-        <f t="shared" si="10"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
       </c>
       <c r="T6" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
+        <f t="shared" si="2"/>
+        <v>Informação</v>
       </c>
       <c r="U6" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V6" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="W6" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="3"/>
         <v>Key-MOT-6</v>
       </c>
       <c r="X6" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="Y6" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="Z6" s="36" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="AA6" s="31" t="str">
-        <f t="shared" ref="AA6" si="24">_xlfn.TRANSLATE(P6,"pt","en")</f>
-        <v>Direct drive motor</v>
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3086,16 +2814,16 @@
         <v>44</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="65" t="s">
-        <v>127</v>
+        <v>166</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>9</v>
@@ -3113,62 +2841,61 @@
         <v>9</v>
       </c>
       <c r="L7" s="35" t="str">
-        <f t="shared" ref="L7:M14" si="25">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:L9" si="5">CONCATENATE("", C7)</f>
         <v>Motricidade</v>
       </c>
       <c r="M7" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="M7:M9" si="6">CONCATENATE("", D7)</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N7" s="35" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N7:N9" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Maquinária</v>
       </c>
       <c r="O7" s="31" t="str">
-        <f t="shared" si="19"/>
-        <v>Máquina.Motriz</v>
+        <f>IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),F7)</f>
+        <v>Motor.de.Combustão</v>
       </c>
       <c r="P7" s="31" t="s">
         <v>130</v>
       </c>
       <c r="Q7" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="37" t="str">
+        <f t="shared" ref="S7:S20" si="8">SUBSTITUTE(C7, "_", " ")</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="T7" s="37" t="str">
+        <f t="shared" ref="T7:T20" si="9">SUBSTITUTE(D7, "_", " ")</f>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U7" s="37" t="str">
+        <f t="shared" ref="U7:U20" si="10">SUBSTITUTE(E7, "_", " ")</f>
+        <v>Maquinária</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="W7" s="68" t="str">
+        <f t="shared" ref="W7:W20" si="11">CONCATENATE("Key-MOT-",A7)</f>
+        <v>Key-MOT-7</v>
+      </c>
+      <c r="X7" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="R7" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="37" t="str">
-        <f t="shared" si="10"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="T7" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U7" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V7" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W7" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-7</v>
-      </c>
-      <c r="X7" s="31" t="s">
-        <v>144</v>
-      </c>
       <c r="Y7" s="30" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="Z7" s="36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AA7" s="31" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through combustion</v>
+        <f t="shared" ref="AA7:AA9" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <v>Combustion engine</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3179,16 +2906,16 @@
         <v>44</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>125</v>
+        <v>166</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>113</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>9</v>
@@ -3206,62 +2933,62 @@
         <v>9</v>
       </c>
       <c r="L8" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L8" si="13">CONCATENATE("", C8)</f>
         <v>Motricidade</v>
       </c>
       <c r="M8" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="M8" si="14">CONCATENATE("", D8)</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N8" s="35" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N8" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Maquinária</v>
       </c>
       <c r="O8" s="31" t="str">
-        <f t="shared" si="19"/>
-        <v>Máquina.de.Combustão.Externa</v>
+        <f t="shared" ref="O8:O20" si="16">IF(ISNUMBER(FIND("Ifc",F8)),CONCATENATE("Classe IFC:   ",F8),F8)</f>
+        <v>Motor.de.Acoplamento</v>
       </c>
       <c r="P8" s="31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="R8" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="37" t="str">
+        <f t="shared" si="8"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T8" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U8" s="37" t="str">
         <f t="shared" si="10"/>
+        <v>Maquinária</v>
+      </c>
+      <c r="V8" s="37" t="str">
+        <f t="shared" ref="V8:V20" si="17">SUBSTITUTE(C8, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="T8" s="37" t="str">
+      <c r="W8" s="68" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U8" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V8" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W8" s="68" t="str">
-        <f t="shared" si="14"/>
         <v>Key-MOT-8</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="Z8" s="36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AA8" s="31" t="str">
-        <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through external combustion</v>
+        <f t="shared" ref="AA8" si="18">_xlfn.TRANSLATE(P8,"pt","en")</f>
+        <v>Coupling motor</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3272,16 +2999,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="65" t="s">
-        <v>126</v>
+        <v>166</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>115</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>9</v>
@@ -3299,62 +3026,62 @@
         <v>9</v>
       </c>
       <c r="L9" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="5"/>
         <v>Motricidade</v>
       </c>
       <c r="M9" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="6"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N9" s="35" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
+        <f t="shared" si="7"/>
         <v>Maquinária</v>
       </c>
       <c r="O9" s="31" t="str">
-        <f t="shared" si="19"/>
-        <v>Máquina.de.Combustão.Interna</v>
+        <f t="shared" si="16"/>
+        <v>Motor.de.Acionamento.Correia</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="R9" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="37" t="str">
+        <f t="shared" si="8"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T9" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U9" s="37" t="str">
         <f t="shared" si="10"/>
+        <v>Maquinária</v>
+      </c>
+      <c r="V9" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="T9" s="37" t="str">
+      <c r="W9" s="68" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U9" s="37" t="str">
+        <v>Key-MOT-9</v>
+      </c>
+      <c r="X9" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z9" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA9" s="31" t="str">
         <f t="shared" si="12"/>
-        <v>Maquinária</v>
-      </c>
-      <c r="V9" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W9" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-9</v>
-      </c>
-      <c r="X9" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y9" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z9" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA9" s="31" t="str">
-        <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through internal combustion</v>
+        <v>Belt drive motor</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3365,16 +3092,16 @@
         <v>44</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="65" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>114</v>
       </c>
       <c r="G10" s="39" t="s">
         <v>9</v>
@@ -3392,62 +3119,62 @@
         <v>9</v>
       </c>
       <c r="L10" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L10" si="19">CONCATENATE("", C10)</f>
         <v>Motricidade</v>
       </c>
       <c r="M10" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="M10" si="20">CONCATENATE("", D10)</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N10" s="35" t="str">
-        <f t="shared" ref="N10:N12" si="26">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E10),"."," ")," De "," de "))</f>
-        <v>Maquinária de Elevação</v>
+        <f t="shared" ref="N10" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E10),"."," ")," De "," de "))</f>
+        <v>Maquinária</v>
       </c>
       <c r="O10" s="31" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
-        <v>Elevador.Hidráulico</v>
+        <f t="shared" si="16"/>
+        <v>Motor.de.Acionamento.Direto</v>
       </c>
       <c r="P10" s="31" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="Q10" s="31" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="R10" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="37" t="str">
-        <f t="shared" ref="S10:S15" si="27">SUBSTITUTE(C10, "_", " ")</f>
+        <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
       <c r="T10" s="37" t="str">
-        <f t="shared" ref="T10:T15" si="28">SUBSTITUTE(D10, "_", " ")</f>
+        <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="U10" s="37" t="str">
-        <f t="shared" ref="U10:U15" si="29">SUBSTITUTE(E10, "_", " ")</f>
-        <v>Maquinária.de.Elevação</v>
+        <f t="shared" si="10"/>
+        <v>Maquinária</v>
       </c>
       <c r="V10" s="37" t="str">
-        <f t="shared" ref="V10:V15" si="30">SUBSTITUTE(C10, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
       <c r="W10" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>Key-MOT-10</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="Y10" s="30" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="Z10" s="36" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="AA10" s="31" t="str">
-        <f t="shared" ref="AA10:AA12" si="31">_xlfn.TRANSLATE(P10,"pt","en")</f>
-        <v>Elevator to a few floors without carrying heavy loads</v>
+        <f t="shared" ref="AA10" si="22">_xlfn.TRANSLATE(P10,"pt","en")</f>
+        <v>Direct drive motor</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3458,17 +3185,17 @@
         <v>44</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="65" t="s">
         <v>166</v>
       </c>
+      <c r="F11" s="64" t="s">
+        <v>123</v>
+      </c>
       <c r="G11" s="39" t="s">
         <v>9</v>
       </c>
@@ -3485,62 +3212,62 @@
         <v>9</v>
       </c>
       <c r="L11" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L11:M18" si="23">CONCATENATE("", C11)</f>
         <v>Motricidade</v>
       </c>
       <c r="M11" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N11" s="35" t="str">
-        <f t="shared" si="26"/>
-        <v>Maquinária de Elevação</v>
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <v>Maquinária</v>
       </c>
       <c r="O11" s="31" t="str">
-        <f t="shared" ref="O11:O15" si="32">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),F11)</f>
-        <v>Elevador.MR</v>
+        <f t="shared" si="16"/>
+        <v>Máquina.Motriz</v>
       </c>
       <c r="P11" s="31" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="Q11" s="31" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="R11" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="37" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
       <c r="T11" s="37" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="U11" s="37" t="str">
-        <f t="shared" si="29"/>
-        <v>Maquinária.de.Elevação</v>
+        <f t="shared" si="10"/>
+        <v>Maquinária</v>
       </c>
       <c r="V11" s="37" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
       <c r="W11" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>Key-MOT-11</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="Y11" s="30" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="Z11" s="36" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="AA11" s="31" t="str">
-        <f t="shared" si="31"/>
-        <v>Traction Elevator with Machine Room</v>
+        <f>_xlfn.TRANSLATE(P11,"pt","en")</f>
+        <v>Engine that converts fuel into mechanical energy through combustion</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3551,89 +3278,89 @@
         <v>44</v>
       </c>
       <c r="C12" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="M12" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="N12" s="35" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E12),"."," ")," De "," de "))</f>
+        <v>Maquinária</v>
+      </c>
+      <c r="O12" s="31" t="str">
+        <f t="shared" si="16"/>
+        <v>Máquina.de.Combustão.Externa</v>
+      </c>
+      <c r="P12" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q12" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="R12" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="37" t="str">
+        <f t="shared" si="8"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T12" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U12" s="37" t="str">
+        <f t="shared" si="10"/>
+        <v>Maquinária</v>
+      </c>
+      <c r="V12" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="W12" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-12</v>
+      </c>
+      <c r="X12" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="35" t="str">
-        <f t="shared" si="25"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="M12" s="35" t="str">
-        <f t="shared" si="25"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="N12" s="35" t="str">
-        <f t="shared" si="26"/>
-        <v>Maquinária de Elevação</v>
-      </c>
-      <c r="O12" s="31" t="str">
-        <f t="shared" si="32"/>
-        <v>Elevador.MRL</v>
-      </c>
-      <c r="P12" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q12" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="R12" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="37" t="str">
-        <f t="shared" si="27"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="T12" s="37" t="str">
-        <f t="shared" si="28"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U12" s="37" t="str">
-        <f t="shared" si="29"/>
-        <v>Maquinária.de.Elevação</v>
-      </c>
-      <c r="V12" s="37" t="str">
-        <f t="shared" si="30"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W12" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-12</v>
-      </c>
-      <c r="X12" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y12" s="30" t="s">
-        <v>185</v>
-      </c>
       <c r="Z12" s="36" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="AA12" s="31" t="str">
-        <f t="shared" si="31"/>
-        <v>Elevator with hoisting pulley without machine room</v>
+        <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
+        <v>Engine that converts fuel into mechanical energy through external combustion</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3644,16 +3371,16 @@
         <v>44</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>174</v>
+        <v>166</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>122</v>
       </c>
       <c r="G13" s="39" t="s">
         <v>9</v>
@@ -3671,62 +3398,62 @@
         <v>9</v>
       </c>
       <c r="L13" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>Motricidade</v>
       </c>
       <c r="M13" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N13" s="35" t="str">
         <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
-        <v>Maquinária de Elevação</v>
+        <v>Maquinária</v>
       </c>
       <c r="O13" s="31" t="str">
-        <f t="shared" ref="O13:O14" si="33">IF(ISNUMBER(FIND("Ifc",F13)),CONCATENATE("Classe IFC:   ",F13),F13)</f>
-        <v>Plataforma</v>
+        <f t="shared" si="16"/>
+        <v>Máquina.de.Combustão.Interna</v>
       </c>
       <c r="P13" s="31" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="Q13" s="31" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="R13" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="37" t="str">
-        <f t="shared" ref="S13:S14" si="34">SUBSTITUTE(C13, "_", " ")</f>
+        <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
       <c r="T13" s="37" t="str">
-        <f t="shared" ref="T13:T14" si="35">SUBSTITUTE(D13, "_", " ")</f>
+        <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="U13" s="37" t="str">
-        <f t="shared" ref="U13:U14" si="36">SUBSTITUTE(E13, "_", " ")</f>
-        <v>Maquinária.de.Elevação</v>
+        <f t="shared" si="10"/>
+        <v>Maquinária</v>
       </c>
       <c r="V13" s="37" t="str">
-        <f t="shared" ref="V13:V14" si="37">SUBSTITUTE(C13, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
       <c r="W13" s="68" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>Key-MOT-13</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="Z13" s="36" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="AA13" s="31" t="str">
         <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
-        <v>Lifting Platform</v>
+        <v>Engine that converts fuel into mechanical energy through internal combustion</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3737,16 +3464,16 @@
         <v>44</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F14" s="65" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>165</v>
       </c>
       <c r="G14" s="39" t="s">
         <v>9</v>
@@ -3764,62 +3491,62 @@
         <v>9</v>
       </c>
       <c r="L14" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>Motricidade</v>
       </c>
       <c r="M14" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N14" s="35" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N14:N16" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
         <v>Maquinária de Elevação</v>
       </c>
       <c r="O14" s="31" t="str">
-        <f t="shared" si="33"/>
-        <v>Plataforma.Articulada</v>
+        <f>IF(ISNUMBER(FIND("Ifc",F14)),CONCATENATE("Classe IFC:   ",F14),F14)</f>
+        <v>Elevador.Hidráulico</v>
       </c>
       <c r="P14" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q14" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="R14" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="37" t="str">
+        <f t="shared" ref="S14:S19" si="25">SUBSTITUTE(C14, "_", " ")</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="T14" s="37" t="str">
+        <f t="shared" ref="T14:T19" si="26">SUBSTITUTE(D14, "_", " ")</f>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U14" s="37" t="str">
+        <f t="shared" ref="U14:U19" si="27">SUBSTITUTE(E14, "_", " ")</f>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V14" s="37" t="str">
+        <f t="shared" ref="V14:V19" si="28">SUBSTITUTE(C14, "_", " ")</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="W14" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-14</v>
+      </c>
+      <c r="X14" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y14" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z14" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q14" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="R14" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="37" t="str">
-        <f t="shared" si="34"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="T14" s="37" t="str">
-        <f t="shared" si="35"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U14" s="37" t="str">
-        <f t="shared" si="36"/>
-        <v>Maquinária.de.Elevação</v>
-      </c>
-      <c r="V14" s="37" t="str">
-        <f t="shared" si="37"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W14" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-14</v>
-      </c>
-      <c r="X14" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y14" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z14" s="36" t="s">
-        <v>188</v>
-      </c>
       <c r="AA14" s="31" t="str">
-        <f>_xlfn.TRANSLATE(P14,"pt","en")</f>
-        <v>Articulated lifting platform</v>
+        <f t="shared" ref="AA14:AA16" si="29">_xlfn.TRANSLATE(P14,"pt","en")</f>
+        <v>Elevator to a few floors without carrying heavy loads</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3830,16 +3557,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F15" s="65" t="s">
-        <v>176</v>
+        <v>168</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>162</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>9</v>
@@ -3857,62 +3584,62 @@
         <v>9</v>
       </c>
       <c r="L15" s="35" t="str">
-        <f t="shared" ref="L15" si="38">CONCATENATE("", C15)</f>
+        <f t="shared" si="23"/>
         <v>Motricidade</v>
       </c>
       <c r="M15" s="35" t="str">
-        <f t="shared" ref="M15" si="39">CONCATENATE("", D15)</f>
+        <f t="shared" si="23"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
       <c r="N15" s="35" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" si="24"/>
         <v>Maquinária de Elevação</v>
       </c>
       <c r="O15" s="31" t="str">
-        <f t="shared" si="32"/>
-        <v>Plataforma.Cesto</v>
+        <f t="shared" ref="O15:O19" si="30">IF(ISNUMBER(FIND("Ifc",F15)),CONCATENATE("Classe IFC:   ",F15),F15)</f>
+        <v>Elevador.MR</v>
       </c>
       <c r="P15" s="31" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="Q15" s="31" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="R15" s="36" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="37" t="str">
+        <f t="shared" si="25"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T15" s="37" t="str">
+        <f t="shared" si="26"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U15" s="37" t="str">
         <f t="shared" si="27"/>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V15" s="37" t="str">
+        <f t="shared" si="28"/>
         <v>Motricidade</v>
       </c>
-      <c r="T15" s="37" t="str">
-        <f t="shared" si="28"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U15" s="37" t="str">
+      <c r="W15" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-15</v>
+      </c>
+      <c r="X15" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y15" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z15" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA15" s="31" t="str">
         <f t="shared" si="29"/>
-        <v>Maquinária.de.Elevação</v>
-      </c>
-      <c r="V15" s="37" t="str">
-        <f t="shared" si="30"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W15" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-15</v>
-      </c>
-      <c r="X15" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y15" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z15" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA15" s="31" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Basket lifting platform</v>
+        <v>Traction Elevator with Machine Room</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3923,140 +3650,530 @@
         <v>44</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="G16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="M16" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="N16" s="35" t="str">
+        <f t="shared" si="24"/>
+        <v>Maquinária de Elevação</v>
+      </c>
+      <c r="O16" s="31" t="str">
+        <f t="shared" si="30"/>
+        <v>Elevador.MRL</v>
+      </c>
+      <c r="P16" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q16" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="R16" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="37" t="str">
+        <f t="shared" si="25"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T16" s="37" t="str">
+        <f t="shared" si="26"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U16" s="37" t="str">
+        <f t="shared" si="27"/>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V16" s="37" t="str">
+        <f t="shared" si="28"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="W16" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-16</v>
+      </c>
+      <c r="X16" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y16" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z16" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA16" s="31" t="str">
+        <f t="shared" si="29"/>
+        <v>Elevator with hoisting pulley without machine room</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="33">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="M17" s="35" t="str">
+        <f t="shared" si="23"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="N17" s="35" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
+        <v>Maquinária de Elevação</v>
+      </c>
+      <c r="O17" s="31" t="str">
+        <f t="shared" ref="O17:O18" si="31">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
+        <v>Plataforma</v>
+      </c>
+      <c r="P17" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q17" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="R17" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="37" t="str">
+        <f t="shared" ref="S17:S18" si="32">SUBSTITUTE(C17, "_", " ")</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="T17" s="37" t="str">
+        <f t="shared" ref="T17:T18" si="33">SUBSTITUTE(D17, "_", " ")</f>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U17" s="37" t="str">
+        <f t="shared" ref="U17:U18" si="34">SUBSTITUTE(E17, "_", " ")</f>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V17" s="37" t="str">
+        <f t="shared" ref="V17:V18" si="35">SUBSTITUTE(C17, "_", " ")</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="W17" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-17</v>
+      </c>
+      <c r="X17" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y17" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z17" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA17" s="31" t="str">
+        <f>_xlfn.TRANSLATE(P17,"pt","en")</f>
+        <v>Lifting Platform</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="33">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="F16" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="35" t="str">
-        <f t="shared" ref="L16:M16" si="40">CONCATENATE("", C16)</f>
+      <c r="G18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="35" t="str">
+        <f t="shared" si="23"/>
         <v>Motricidade</v>
       </c>
-      <c r="M16" s="35" t="str">
-        <f t="shared" si="40"/>
+      <c r="M18" s="35" t="str">
+        <f t="shared" si="23"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="N16" s="35" t="str">
-        <f t="shared" ref="N16" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+      <c r="N18" s="35" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
+        <v>Maquinária de Elevação</v>
+      </c>
+      <c r="O18" s="31" t="str">
+        <f t="shared" si="31"/>
+        <v>Plataforma.Articulada</v>
+      </c>
+      <c r="P18" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q18" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="R18" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="37" t="str">
+        <f t="shared" si="32"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T18" s="37" t="str">
+        <f t="shared" si="33"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U18" s="37" t="str">
+        <f t="shared" si="34"/>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V18" s="37" t="str">
+        <f t="shared" si="35"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="W18" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-18</v>
+      </c>
+      <c r="X18" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y18" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z18" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA18" s="31" t="str">
+        <f>_xlfn.TRANSLATE(P18,"pt","en")</f>
+        <v>Articulated lifting platform</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="35" t="str">
+        <f t="shared" ref="L19" si="36">CONCATENATE("", C19)</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="M19" s="35" t="str">
+        <f t="shared" ref="M19" si="37">CONCATENATE("", D19)</f>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="N19" s="35" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <v>Maquinária de Elevação</v>
+      </c>
+      <c r="O19" s="31" t="str">
+        <f t="shared" si="30"/>
+        <v>Plataforma.Cesto</v>
+      </c>
+      <c r="P19" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q19" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="R19" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="37" t="str">
+        <f t="shared" si="25"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T19" s="37" t="str">
+        <f t="shared" si="26"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U19" s="37" t="str">
+        <f t="shared" si="27"/>
+        <v>Maquinária.de.Elevação</v>
+      </c>
+      <c r="V19" s="37" t="str">
+        <f t="shared" si="28"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="W19" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-MOT-19</v>
+      </c>
+      <c r="X19" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y19" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z19" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA19" s="31" t="str">
+        <f>_xlfn.TRANSLATE(P19,"pt","en")</f>
+        <v>Basket lifting platform</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="33">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="35" t="str">
+        <f t="shared" ref="L20:M20" si="38">CONCATENATE("", C20)</f>
+        <v>Motricidade</v>
+      </c>
+      <c r="M20" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="N20" s="35" t="str">
+        <f t="shared" ref="N20" si="39">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
         <v>Acessórios Maquinária</v>
       </c>
-      <c r="O16" s="31" t="str">
-        <f t="shared" si="19"/>
+      <c r="O20" s="31" t="str">
+        <f t="shared" si="16"/>
         <v>Acessório.Maquinária</v>
       </c>
-      <c r="P16" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q16" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="R16" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="37" t="str">
+      <c r="P20" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q20" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="R20" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="37" t="str">
+        <f t="shared" si="8"/>
+        <v>Motricidade</v>
+      </c>
+      <c r="T20" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Elementos.de.Força.Motriz</v>
+      </c>
+      <c r="U20" s="37" t="str">
         <f t="shared" si="10"/>
+        <v>Acessórios.Maquinária</v>
+      </c>
+      <c r="V20" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="T16" s="37" t="str">
+      <c r="W20" s="68" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Força.Motriz</v>
-      </c>
-      <c r="U16" s="37" t="str">
-        <f t="shared" si="12"/>
-        <v>Acessórios.Maquinária</v>
-      </c>
-      <c r="V16" s="37" t="str">
-        <f t="shared" si="13"/>
-        <v>Motricidade</v>
-      </c>
-      <c r="W16" s="68" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-MOT-16</v>
-      </c>
-      <c r="X16" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y16" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z16" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA16" s="31" t="str">
-        <f t="shared" ref="AA16" si="42">_xlfn.TRANSLATE(P16,"pt","en")</f>
+        <v>Key-MOT-20</v>
+      </c>
+      <c r="X20" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y20" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z20" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA20" s="31" t="str">
+        <f t="shared" ref="AA20" si="40">_xlfn.TRANSLATE(P20,"pt","en")</f>
         <v>Mechanical Accessory</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA741">
-    <sortCondition ref="F2:F741"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA745">
+    <sortCondition ref="F7:F745"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:O1 R1:X1 Z1 AA3:AA15">
-    <cfRule type="cellIs" dxfId="60" priority="211" operator="equal">
+  <conditionalFormatting sqref="AA7:AA19">
+    <cfRule type="cellIs" dxfId="31" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
+    <cfRule type="cellIs" dxfId="30" priority="223" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="59" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1659"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="58" priority="1663"/>
+  <conditionalFormatting sqref="F7:F10">
+    <cfRule type="duplicateValues" dxfId="28" priority="2057"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="57" priority="2045"/>
+  <conditionalFormatting sqref="F11:F13">
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="56" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="16"/>
+  <conditionalFormatting sqref="F14:F19">
+    <cfRule type="duplicateValues" dxfId="21" priority="2094"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="50" priority="119"/>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="20" priority="131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F1048576 F1:F2">
-    <cfRule type="duplicateValues" dxfId="49" priority="1990"/>
+  <conditionalFormatting sqref="F20:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="19" priority="2002"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F1048576 F2">
-    <cfRule type="duplicateValues" dxfId="48" priority="2000"/>
+  <conditionalFormatting sqref="F20:F1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2019"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2062"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="2006"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="2007"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="2008"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="2050"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X3:X16">
-    <cfRule type="containsText" dxfId="43" priority="38" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",X3)))</formula>
+  <conditionalFormatting sqref="X7:X20">
+    <cfRule type="containsText" dxfId="13" priority="50" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",X7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F15">
-    <cfRule type="duplicateValues" dxfId="34" priority="2082"/>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4271,7 +4388,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4332,7 +4449,7 @@
       <c r="G1" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="59" t="s">
         <v>77</v>
       </c>
       <c r="I1" s="20" t="s">
@@ -4374,54 +4491,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="H2" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="J2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="L2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="61" t="s">
+      <c r="N2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="61" t="s">
+      <c r="R2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="25" t="s">
@@ -4432,472 +4549,472 @@
       <c r="A3" s="21">
         <v>3</v>
       </c>
-      <c r="B3" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>109</v>
+      <c r="B3" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O3" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P3" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R3" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O3" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P3" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R3" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S3" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
-      <c r="B4" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>109</v>
+      <c r="B4" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O4" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P4" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R4" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O4" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P4" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R4" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S4" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
-      <c r="B5" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="62" t="s">
-        <v>109</v>
+      <c r="B5" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O5" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P5" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R5" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O5" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P5" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R5" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S5" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
-      <c r="B6" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="62" t="s">
-        <v>109</v>
+      <c r="B6" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O6" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P6" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R6" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O6" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P6" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R6" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S6" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="62" t="s">
-        <v>109</v>
+      <c r="B7" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H7" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O7" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P7" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R7" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O7" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P7" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R7" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S7" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
-      <c r="B8" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>109</v>
+      <c r="B8" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O8" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P8" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R8" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O8" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P8" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R8" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S8" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>109</v>
+      <c r="B9" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H9" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O9" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P9" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R9" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O9" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P9" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R9" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S9" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
-      <c r="B10" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="62" t="s">
-        <v>109</v>
+      <c r="B10" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>105</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="H10" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="P10" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="R10" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="O10" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R10" s="61" t="s">
-        <v>108</v>
-      </c>
       <c r="S10" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4970,22 +5087,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="31" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="27" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/MOTO/Ontologia_Motriz.xlsx
+++ b/Versão5/MOTO/Ontologia_Motriz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBB5D20-9872-4527-9FD2-131DB9D6C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93E9142-090D-49CE-8C12-D9C78A2A8A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -374,9 +374,6 @@
     <t>CTI_Projeto_01</t>
   </si>
   <si>
-    <t>fabricante</t>
-  </si>
-  <si>
     <t>"Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
@@ -666,6 +663,9 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>quem.fabricou</t>
   </si>
 </sst>
 </file>
@@ -1214,15 +1214,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -1289,6 +1281,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1326,22 +1334,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1986,7 +1978,7 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>93</v>
@@ -2142,7 +2134,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>93</v>
@@ -2154,7 +2146,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46139.506402662038</v>
+        <v>46213.788100925929</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>93</v>
@@ -2198,7 +2190,7 @@
         <v>72</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>93</v>
@@ -2209,7 +2201,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>94</v>
@@ -2351,7 +2343,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>83</v>
@@ -2360,10 +2352,10 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G2" s="39" t="s">
         <v>9</v>
@@ -2397,7 +2389,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="31" t="s">
         <v>85</v>
@@ -2418,7 +2410,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W2" s="68" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-MOT-",A2)</f>
@@ -2443,7 +2435,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>83</v>
@@ -2452,10 +2444,10 @@
         <v>84</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>9</v>
@@ -2489,7 +2481,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q3" s="31" t="s">
         <v>85</v>
@@ -2510,7 +2502,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W3" s="68" t="str">
         <f t="shared" si="3"/>
@@ -2535,7 +2527,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C4" s="64" t="s">
         <v>83</v>
@@ -2544,10 +2536,10 @@
         <v>84</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>9</v>
@@ -2581,7 +2573,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q4" s="31" t="s">
         <v>85</v>
@@ -2602,7 +2594,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W4" s="68" t="str">
         <f t="shared" si="3"/>
@@ -2627,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C5" s="64" t="s">
         <v>83</v>
@@ -2636,10 +2628,10 @@
         <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>9</v>
@@ -2673,7 +2665,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q5" s="31" t="s">
         <v>85</v>
@@ -2694,7 +2686,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W5" s="68" t="str">
         <f t="shared" si="3"/>
@@ -2719,7 +2711,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C6" s="64" t="s">
         <v>83</v>
@@ -2728,10 +2720,10 @@
         <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>9</v>
@@ -2765,7 +2757,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="31" t="s">
         <v>85</v>
@@ -2786,7 +2778,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W6" s="68" t="str">
         <f t="shared" si="3"/>
@@ -2814,16 +2806,16 @@
         <v>44</v>
       </c>
       <c r="C7" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="64" t="s">
         <v>116</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="64" t="s">
-        <v>117</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>9</v>
@@ -2857,10 +2849,10 @@
         <v>Motor.de.Combustão</v>
       </c>
       <c r="P7" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q7" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R7" s="36" t="s">
         <v>9</v>
@@ -2878,20 +2870,20 @@
         <v>Maquinária</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W7" s="68" t="str">
         <f t="shared" ref="W7:W20" si="11">CONCATENATE("Key-MOT-",A7)</f>
         <v>Key-MOT-7</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y7" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z7" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA7" s="31" t="str">
         <f t="shared" ref="AA7:AA9" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
@@ -2906,16 +2898,16 @@
         <v>44</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>9</v>
@@ -2949,10 +2941,10 @@
         <v>Motor.de.Acoplamento</v>
       </c>
       <c r="P8" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R8" s="36" t="s">
         <v>9</v>
@@ -2978,13 +2970,13 @@
         <v>Key-MOT-8</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Z8" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA8" s="31" t="str">
         <f t="shared" ref="AA8" si="18">_xlfn.TRANSLATE(P8,"pt","en")</f>
@@ -2999,16 +2991,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F9" s="64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>9</v>
@@ -3042,10 +3034,10 @@
         <v>Motor.de.Acionamento.Correia</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R9" s="36" t="s">
         <v>9</v>
@@ -3071,13 +3063,13 @@
         <v>Key-MOT-9</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y9" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z9" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA9" s="31" t="str">
         <f t="shared" si="12"/>
@@ -3092,16 +3084,16 @@
         <v>44</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="39" t="s">
         <v>9</v>
@@ -3135,10 +3127,10 @@
         <v>Motor.de.Acionamento.Direto</v>
       </c>
       <c r="P10" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q10" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R10" s="36" t="s">
         <v>9</v>
@@ -3164,13 +3156,13 @@
         <v>Key-MOT-10</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y10" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z10" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA10" s="31" t="str">
         <f t="shared" ref="AA10" si="22">_xlfn.TRANSLATE(P10,"pt","en")</f>
@@ -3185,16 +3177,16 @@
         <v>44</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F11" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="39" t="s">
         <v>9</v>
@@ -3228,10 +3220,10 @@
         <v>Máquina.Motriz</v>
       </c>
       <c r="P11" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q11" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R11" s="36" t="s">
         <v>9</v>
@@ -3257,13 +3249,13 @@
         <v>Key-MOT-11</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y11" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z11" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA11" s="31" t="str">
         <f>_xlfn.TRANSLATE(P11,"pt","en")</f>
@@ -3278,16 +3270,16 @@
         <v>44</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F12" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G12" s="39" t="s">
         <v>9</v>
@@ -3321,10 +3313,10 @@
         <v>Máquina.de.Combustão.Externa</v>
       </c>
       <c r="P12" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R12" s="36" t="s">
         <v>9</v>
@@ -3350,13 +3342,13 @@
         <v>Key-MOT-12</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y12" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z12" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA12" s="31" t="str">
         <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
@@ -3371,16 +3363,16 @@
         <v>44</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F13" s="64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="39" t="s">
         <v>9</v>
@@ -3414,10 +3406,10 @@
         <v>Máquina.de.Combustão.Interna</v>
       </c>
       <c r="P13" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q13" s="31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R13" s="36" t="s">
         <v>9</v>
@@ -3443,13 +3435,13 @@
         <v>Key-MOT-13</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z13" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA13" s="31" t="str">
         <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
@@ -3464,16 +3456,16 @@
         <v>44</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F14" s="64" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G14" s="39" t="s">
         <v>9</v>
@@ -3507,10 +3499,10 @@
         <v>Elevador.Hidráulico</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q14" s="31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R14" s="36" t="s">
         <v>9</v>
@@ -3536,13 +3528,13 @@
         <v>Key-MOT-14</v>
       </c>
       <c r="X14" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y14" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z14" s="36" t="s">
         <v>182</v>
-      </c>
-      <c r="Y14" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z14" s="36" t="s">
-        <v>183</v>
       </c>
       <c r="AA14" s="31" t="str">
         <f t="shared" ref="AA14:AA16" si="29">_xlfn.TRANSLATE(P14,"pt","en")</f>
@@ -3557,16 +3549,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F15" s="64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>9</v>
@@ -3600,10 +3592,10 @@
         <v>Elevador.MR</v>
       </c>
       <c r="P15" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q15" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R15" s="36" t="s">
         <v>9</v>
@@ -3629,13 +3621,13 @@
         <v>Key-MOT-15</v>
       </c>
       <c r="X15" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y15" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z15" s="36" t="s">
         <v>182</v>
-      </c>
-      <c r="Y15" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z15" s="36" t="s">
-        <v>183</v>
       </c>
       <c r="AA15" s="31" t="str">
         <f t="shared" si="29"/>
@@ -3650,16 +3642,16 @@
         <v>44</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16" s="64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G16" s="39" t="s">
         <v>9</v>
@@ -3693,10 +3685,10 @@
         <v>Elevador.MRL</v>
       </c>
       <c r="P16" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q16" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R16" s="36" t="s">
         <v>9</v>
@@ -3722,13 +3714,13 @@
         <v>Key-MOT-16</v>
       </c>
       <c r="X16" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y16" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z16" s="36" t="s">
         <v>182</v>
-      </c>
-      <c r="Y16" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z16" s="36" t="s">
-        <v>183</v>
       </c>
       <c r="AA16" s="31" t="str">
         <f t="shared" si="29"/>
@@ -3743,16 +3735,16 @@
         <v>44</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F17" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G17" s="39" t="s">
         <v>9</v>
@@ -3786,10 +3778,10 @@
         <v>Plataforma</v>
       </c>
       <c r="P17" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q17" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R17" s="36" t="s">
         <v>9</v>
@@ -3815,13 +3807,13 @@
         <v>Key-MOT-17</v>
       </c>
       <c r="X17" s="31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y17" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z17" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA17" s="31" t="str">
         <f>_xlfn.TRANSLATE(P17,"pt","en")</f>
@@ -3836,16 +3828,16 @@
         <v>44</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F18" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G18" s="39" t="s">
         <v>9</v>
@@ -3879,10 +3871,10 @@
         <v>Plataforma.Articulada</v>
       </c>
       <c r="P18" s="31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q18" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R18" s="36" t="s">
         <v>9</v>
@@ -3908,13 +3900,13 @@
         <v>Key-MOT-18</v>
       </c>
       <c r="X18" s="31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y18" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z18" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA18" s="31" t="str">
         <f>_xlfn.TRANSLATE(P18,"pt","en")</f>
@@ -3929,16 +3921,16 @@
         <v>44</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F19" s="64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G19" s="39" t="s">
         <v>9</v>
@@ -3972,10 +3964,10 @@
         <v>Plataforma.Cesto</v>
       </c>
       <c r="P19" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q19" s="31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R19" s="36" t="s">
         <v>9</v>
@@ -4001,13 +3993,13 @@
         <v>Key-MOT-19</v>
       </c>
       <c r="X19" s="31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y19" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z19" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA19" s="31" t="str">
         <f>_xlfn.TRANSLATE(P19,"pt","en")</f>
@@ -4022,16 +4014,16 @@
         <v>44</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="51" t="s">
         <v>157</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>158</v>
       </c>
       <c r="G20" s="50" t="s">
         <v>9</v>
@@ -4065,10 +4057,10 @@
         <v>Acessório.Maquinária</v>
       </c>
       <c r="P20" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R20" s="36" t="s">
         <v>9</v>
@@ -4094,13 +4086,13 @@
         <v>Key-MOT-20</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y20" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z20" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA20" s="31" t="str">
         <f t="shared" ref="AA20" si="40">_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -4112,68 +4104,61 @@
     <sortCondition ref="F7:F745"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="31" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="30" priority="223" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="223" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="29" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1659"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F10">
-    <cfRule type="duplicateValues" dxfId="28" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F13">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F19">
-    <cfRule type="duplicateValues" dxfId="21" priority="2094"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="20" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="19" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="2012"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2018"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2019"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2020"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2019"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X7:X20">
-    <cfRule type="containsText" dxfId="13" priority="50" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="8" priority="50" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA19">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4388,7 +4373,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4413,7 +4398,7 @@
     <col min="5" max="5" width="8.15234375" customWidth="1"/>
     <col min="6" max="6" width="5.23046875" customWidth="1"/>
     <col min="7" max="7" width="32.61328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.3046875" customWidth="1"/>
+    <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.3828125" customWidth="1"/>
     <col min="10" max="10" width="4.4609375" customWidth="1"/>
     <col min="11" max="11" width="5.69140625" customWidth="1"/>
@@ -4494,7 +4479,7 @@
         <v>99</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D2" s="61" t="s">
         <v>9</v>
@@ -4506,7 +4491,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>9</v>
@@ -4550,13 +4535,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E3" s="40" t="s">
         <v>99</v>
@@ -4565,43 +4550,43 @@
         <v>78</v>
       </c>
       <c r="G3" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J3" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K3" s="25" t="s">
+      <c r="L3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O3" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P3" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R3" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S3" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L3" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O3" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P3" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R3" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4609,13 +4594,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" s="40" t="s">
         <v>99</v>
@@ -4624,43 +4609,43 @@
         <v>78</v>
       </c>
       <c r="G4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H4" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J4" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K4" s="25" t="s">
+      <c r="L4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O4" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P4" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R4" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S4" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L4" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O4" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P4" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R4" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4668,13 +4653,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D5" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="40" t="s">
         <v>99</v>
@@ -4683,43 +4668,43 @@
         <v>78</v>
       </c>
       <c r="G5" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H5" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="25" t="s">
+      <c r="L5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P5" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R5" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S5" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L5" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O5" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P5" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R5" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4727,13 +4712,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>99</v>
@@ -4742,43 +4727,43 @@
         <v>78</v>
       </c>
       <c r="G6" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J6" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K6" s="25" t="s">
+      <c r="L6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P6" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R6" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L6" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P6" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R6" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S6" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4786,13 +4771,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>99</v>
@@ -4801,43 +4786,43 @@
         <v>78</v>
       </c>
       <c r="G7" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H7" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J7" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K7" s="25" t="s">
+      <c r="L7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P7" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R7" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S7" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L7" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P7" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R7" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4845,13 +4830,13 @@
         <v>8</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="40" t="s">
         <v>99</v>
@@ -4860,43 +4845,43 @@
         <v>78</v>
       </c>
       <c r="G8" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H8" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8" s="25" t="s">
+      <c r="L8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P8" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R8" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S8" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L8" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P8" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R8" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4904,13 +4889,13 @@
         <v>9</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" s="40" t="s">
         <v>99</v>
@@ -4919,43 +4904,43 @@
         <v>78</v>
       </c>
       <c r="G9" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H9" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J9" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K9" s="25" t="s">
+      <c r="L9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O9" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P9" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R9" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L9" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O9" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P9" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R9" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4963,13 +4948,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>99</v>
@@ -4978,43 +4963,43 @@
         <v>78</v>
       </c>
       <c r="G10" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H10" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J10" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K10" s="25" t="s">
+      <c r="L10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="O10" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="P10" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R10" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="S10" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="L10" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="P10" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="R10" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5087,22 +5072,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/MOTO/Ontologia_Motriz.xlsx
+++ b/Versão5/MOTO/Ontologia_Motriz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93E9142-090D-49CE-8C12-D9C78A2A8A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBC686D-D6D7-4B82-A0B2-4FDFE39D9234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46213.788100925929</v>
+        <v>46214.390779050926</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>93</v>
@@ -4391,25 +4391,25 @@
   <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3046875" customWidth="1"/>
-    <col min="4" max="4" width="7.4609375" customWidth="1"/>
-    <col min="5" max="5" width="8.15234375" customWidth="1"/>
-    <col min="6" max="6" width="5.23046875" customWidth="1"/>
-    <col min="7" max="7" width="32.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.3828125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3828125" customWidth="1"/>
-    <col min="10" max="10" width="4.4609375" customWidth="1"/>
-    <col min="11" max="11" width="5.69140625" customWidth="1"/>
-    <col min="12" max="12" width="3.61328125" customWidth="1"/>
+    <col min="9" max="9" width="8.61328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.15234375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="1.921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.4609375" customWidth="1"/>
-    <col min="15" max="15" width="6.3046875" style="38" customWidth="1"/>
-    <col min="16" max="16" width="4.69140625" customWidth="1"/>
-    <col min="17" max="17" width="5.765625" customWidth="1"/>
-    <col min="18" max="18" width="6.765625" customWidth="1"/>
-    <col min="19" max="19" width="11.61328125" customWidth="1"/>
+    <col min="14" max="14" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.61328125" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4455,7 +4455,7 @@
       <c r="N1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="20" t="s">
         <v>79</v>
       </c>
       <c r="P1" s="20" t="s">
@@ -4467,7 +4467,7 @@
       <c r="R1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="S1" s="18" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       <c r="N2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="67" t="s">
+      <c r="O2" s="25" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="60" t="s">
@@ -4526,7 +4526,7 @@
       <c r="R2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="67" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4571,10 +4571,10 @@
         <v>9</v>
       </c>
       <c r="N3" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>102</v>
@@ -4583,10 +4583,10 @@
         <v>151</v>
       </c>
       <c r="R3" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S3" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4630,10 +4630,10 @@
         <v>9</v>
       </c>
       <c r="N4" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O4" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P4" s="60" t="s">
         <v>102</v>
@@ -4642,10 +4642,10 @@
         <v>151</v>
       </c>
       <c r="R4" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S4" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4689,10 +4689,10 @@
         <v>9</v>
       </c>
       <c r="N5" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P5" s="60" t="s">
         <v>102</v>
@@ -4701,10 +4701,10 @@
         <v>151</v>
       </c>
       <c r="R5" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S5" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4748,10 +4748,10 @@
         <v>9</v>
       </c>
       <c r="N6" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O6" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P6" s="60" t="s">
         <v>102</v>
@@ -4760,10 +4760,10 @@
         <v>151</v>
       </c>
       <c r="R6" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S6" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S6" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4807,10 +4807,10 @@
         <v>9</v>
       </c>
       <c r="N7" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O7" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P7" s="60" t="s">
         <v>102</v>
@@ -4819,10 +4819,10 @@
         <v>151</v>
       </c>
       <c r="R7" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S7" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4866,10 +4866,10 @@
         <v>9</v>
       </c>
       <c r="N8" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O8" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P8" s="60" t="s">
         <v>102</v>
@@ -4878,10 +4878,10 @@
         <v>151</v>
       </c>
       <c r="R8" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S8" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4925,10 +4925,10 @@
         <v>9</v>
       </c>
       <c r="N9" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P9" s="60" t="s">
         <v>102</v>
@@ -4937,10 +4937,10 @@
         <v>151</v>
       </c>
       <c r="R9" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S9" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4984,10 +4984,10 @@
         <v>9</v>
       </c>
       <c r="N10" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="O10" s="67" t="s">
-        <v>159</v>
+        <v>103</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="P10" s="60" t="s">
         <v>102</v>
@@ -4996,10 +4996,10 @@
         <v>151</v>
       </c>
       <c r="R10" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>150</v>
+        <v>101</v>
+      </c>
+      <c r="S10" s="67" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/MOTO/Ontologia_Motriz.xlsx
+++ b/Versão5/MOTO/Ontologia_Motriz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBC686D-D6D7-4B82-A0B2-4FDFE39D9234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6756EAE9-437E-4919-B054-6E274D6B9FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="197">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -203,9 +203,6 @@
     <t>000 Traducción Classe 5</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>CTI_Projeto_01</t>
-  </si>
-  <si>
     <t>"Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
@@ -395,9 +389,6 @@
     <t>[ IfcDiscreteAccessory ]</t>
   </si>
   <si>
-    <t>"Nome do fabricante"</t>
-  </si>
-  <si>
     <t>[ IfcMotorConnection ]</t>
   </si>
   <si>
@@ -524,12 +515,6 @@
     <t>"Modelo"</t>
   </si>
   <si>
-    <t>"OST_MechanicalEquipment"</t>
-  </si>
-  <si>
-    <t>"IfcEngine"</t>
-  </si>
-  <si>
     <t>Objetos de Sistemas Mecâninos Motrizes</t>
   </si>
   <si>
@@ -626,18 +611,9 @@
     <t>[ 3E.08.06.10.02 ]</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
@@ -665,7 +641,28 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>quem.fabricou</t>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>quem.fabrica</t>
+  </si>
+  <si>
+    <t>"[ OST_MechanicalEquipment ]"</t>
+  </si>
+  <si>
+    <t>"[ IfcEngine ]"</t>
+  </si>
+  <si>
+    <t>"Nome de um fabricante"</t>
+  </si>
+  <si>
+    <t>CTI_Projeto_A</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1111,18 +1108,9 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1147,18 +1135,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1168,15 +1147,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1201,20 +1174,97 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1944,279 +1994,279 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="47.15234375" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="47" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="B2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="44" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="43" t="s">
+      <c r="B8" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46214.390779050926</v>
-      </c>
-      <c r="C18" s="46" t="s">
+        <v>46216.399269444446</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="43" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="44" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Mechanical Driving Systems</v>
       </c>
-      <c r="C24" s="46" t="s">
-        <v>95</v>
+      <c r="C24" s="43" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2228,153 +2278,154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="3.84375" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" customWidth="1"/>
-    <col min="4" max="4" width="11.3828125" customWidth="1"/>
-    <col min="5" max="5" width="9.921875" customWidth="1"/>
-    <col min="6" max="6" width="14" style="48" customWidth="1"/>
-    <col min="7" max="7" width="6.4609375" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="6.3046875" style="38" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" customWidth="1"/>
-    <col min="13" max="13" width="11.4609375" customWidth="1"/>
-    <col min="14" max="14" width="10.61328125" customWidth="1"/>
-    <col min="15" max="15" width="13.765625" customWidth="1"/>
-    <col min="16" max="17" width="34.765625" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.921875" customWidth="1"/>
-    <col min="20" max="20" width="11.921875" customWidth="1"/>
-    <col min="21" max="21" width="10.23046875" customWidth="1"/>
-    <col min="22" max="22" width="5.69140625" customWidth="1"/>
-    <col min="23" max="23" width="7.3828125" customWidth="1"/>
-    <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.53515625" style="57" customWidth="1"/>
-    <col min="26" max="26" width="7.921875" style="38" customWidth="1"/>
-    <col min="27" max="27" width="40.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="66" customWidth="1"/>
+    <col min="7" max="11" width="8" style="62" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.85546875" style="62" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.85546875" style="62" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" style="67" customWidth="1"/>
+    <col min="26" max="26" width="10.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="54" t="s">
+      <c r="M1" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y1" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z1" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA1" s="39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="59">
         <v>2</v>
       </c>
-      <c r="J1" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="M1" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="S1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y1" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z1" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA1" s="42" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="39" t="s">
+      <c r="E2" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="35" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="35" t="str">
         <f t="shared" si="0"/>
@@ -2382,37 +2433,37 @@
       </c>
       <c r="N2" s="35" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="31" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="Q2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="37" t="str">
+        <v>84</v>
+      </c>
+      <c r="R2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="31" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="37" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="31" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="37" t="str">
+      <c r="U2" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W2" s="68" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W2" s="61" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-MOT-",A2)</f>
         <v>Key-MOT-2</v>
       </c>
@@ -2422,51 +2473,51 @@
       <c r="Y2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="36" t="s">
-        <v>9</v>
+      <c r="Z2" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="AA2" s="31" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="33">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="59">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="39" t="s">
+      <c r="E3" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="35" t="str">
         <f t="shared" si="0"/>
@@ -2474,37 +2525,37 @@
       </c>
       <c r="N3" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="31" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="Q3" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="37" t="str">
+        <v>84</v>
+      </c>
+      <c r="R3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="37" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="31" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="37" t="str">
+      <c r="U3" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W3" s="68" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W3" s="61" t="str">
         <f t="shared" si="3"/>
         <v>Key-MOT-3</v>
       </c>
@@ -2514,7 +2565,7 @@
       <c r="Y3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="36" t="s">
+      <c r="Z3" s="31" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="31" t="str">
@@ -2522,43 +2573,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="33">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="59">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="39" t="s">
+      <c r="E4" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="35" t="str">
         <f t="shared" si="0"/>
@@ -2566,37 +2617,37 @@
       </c>
       <c r="N4" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="31" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="37" t="str">
+        <v>84</v>
+      </c>
+      <c r="R4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="37" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="31" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="37" t="str">
+      <c r="U4" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W4" s="68" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W4" s="61" t="str">
         <f t="shared" si="3"/>
         <v>Key-MOT-4</v>
       </c>
@@ -2606,7 +2657,7 @@
       <c r="Y4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="36" t="s">
+      <c r="Z4" s="31" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="31" t="str">
@@ -2614,43 +2665,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="33">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="59">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>193</v>
-      </c>
-      <c r="G5" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="39" t="s">
+      <c r="E5" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="35" t="str">
         <f t="shared" si="0"/>
@@ -2658,37 +2709,37 @@
       </c>
       <c r="N5" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="31" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="Q5" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R5" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="37" t="str">
+        <v>84</v>
+      </c>
+      <c r="R5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="37" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="31" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="37" t="str">
+      <c r="U5" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W5" s="68" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W5" s="61" t="str">
         <f t="shared" si="3"/>
         <v>Key-MOT-5</v>
       </c>
@@ -2698,7 +2749,7 @@
       <c r="Y5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="Z5" s="31" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="31" t="str">
@@ -2706,43 +2757,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="33">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="39" t="s">
+      <c r="E6" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="35" t="str">
         <f t="shared" si="0"/>
@@ -2750,37 +2801,37 @@
       </c>
       <c r="N6" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R6" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="37" t="str">
+        <v>84</v>
+      </c>
+      <c r="R6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="37" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="31" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="37" t="str">
+      <c r="U6" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W6" s="68" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W6" s="61" t="str">
         <f t="shared" si="3"/>
         <v>Key-MOT-6</v>
       </c>
@@ -2790,7 +2841,7 @@
       <c r="Y6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="36" t="s">
+      <c r="Z6" s="31" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="31" t="str">
@@ -2798,38 +2849,38 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="33">
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="59">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="35" t="str">
@@ -2849,79 +2900,79 @@
         <v>Motor.de.Combustão</v>
       </c>
       <c r="P7" s="31" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q7" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="R7" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="37" t="str">
+        <v>128</v>
+      </c>
+      <c r="R7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="31" t="str">
         <f t="shared" ref="S7:S20" si="8">SUBSTITUTE(C7, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="T7" s="37" t="str">
+      <c r="T7" s="31" t="str">
         <f t="shared" ref="T7:T20" si="9">SUBSTITUTE(D7, "_", " ")</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U7" s="37" t="str">
+      <c r="U7" s="31" t="str">
         <f t="shared" ref="U7:U20" si="10">SUBSTITUTE(E7, "_", " ")</f>
         <v>Maquinária</v>
       </c>
-      <c r="V7" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="W7" s="68" t="str">
+      <c r="V7" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W7" s="61" t="str">
         <f t="shared" ref="W7:W20" si="11">CONCATENATE("Key-MOT-",A7)</f>
         <v>Key-MOT-7</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y7" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z7" s="36" t="s">
-        <v>158</v>
+        <v>105</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA7" s="31" t="str">
         <f t="shared" ref="AA7:AA9" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Combustion engine</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="33">
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="59">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="35" t="str">
@@ -2941,80 +2992,80 @@
         <v>Motor.de.Acoplamento</v>
       </c>
       <c r="P8" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="R8" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="37" t="str">
+        <v>129</v>
+      </c>
+      <c r="R8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T8" s="37" t="str">
+      <c r="T8" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U8" s="37" t="str">
+      <c r="U8" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V8" s="37" t="str">
+      <c r="V8" s="31" t="str">
         <f t="shared" ref="V8:V20" si="17">SUBSTITUTE(C8, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="W8" s="68" t="str">
+      <c r="W8" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-8</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z8" s="36" t="s">
-        <v>158</v>
+        <v>106</v>
+      </c>
+      <c r="Z8" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA8" s="31" t="str">
         <f t="shared" ref="AA8" si="18">_xlfn.TRANSLATE(P8,"pt","en")</f>
         <v>Coupling motor</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="33">
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="59">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="35" t="str">
@@ -3034,80 +3085,80 @@
         <v>Motor.de.Acionamento.Correia</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="R9" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="37" t="str">
+        <v>130</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T9" s="37" t="str">
+      <c r="T9" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U9" s="37" t="str">
+      <c r="U9" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V9" s="37" t="str">
+      <c r="V9" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W9" s="68" t="str">
+      <c r="W9" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-9</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y9" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z9" s="36" t="s">
-        <v>158</v>
+        <v>107</v>
+      </c>
+      <c r="Z9" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA9" s="31" t="str">
         <f t="shared" si="12"/>
         <v>Belt drive motor</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="33">
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="59">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F10" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="35" t="str">
@@ -3127,80 +3178,80 @@
         <v>Motor.de.Acionamento.Direto</v>
       </c>
       <c r="P10" s="31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q10" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="R10" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="37" t="str">
+        <v>131</v>
+      </c>
+      <c r="R10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T10" s="37" t="str">
+      <c r="T10" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U10" s="37" t="str">
+      <c r="U10" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V10" s="37" t="str">
+      <c r="V10" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W10" s="68" t="str">
+      <c r="W10" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-10</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y10" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z10" s="36" t="s">
-        <v>158</v>
+        <v>108</v>
+      </c>
+      <c r="Z10" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA10" s="31" t="str">
         <f t="shared" ref="AA10" si="22">_xlfn.TRANSLATE(P10,"pt","en")</f>
         <v>Direct drive motor</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="33">
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="59">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="35" t="str">
@@ -3220,80 +3271,80 @@
         <v>Máquina.Motriz</v>
       </c>
       <c r="P11" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q11" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="R11" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="37" t="str">
+        <v>132</v>
+      </c>
+      <c r="R11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T11" s="37" t="str">
+      <c r="T11" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U11" s="37" t="str">
+      <c r="U11" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V11" s="37" t="str">
+      <c r="V11" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W11" s="68" t="str">
+      <c r="W11" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-11</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y11" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z11" s="36" t="s">
-        <v>158</v>
+        <v>114</v>
+      </c>
+      <c r="Z11" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA11" s="31" t="str">
         <f>_xlfn.TRANSLATE(P11,"pt","en")</f>
         <v>Engine that converts fuel into mechanical energy through combustion</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="33">
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="35" t="str">
@@ -3313,80 +3364,80 @@
         <v>Máquina.de.Combustão.Externa</v>
       </c>
       <c r="P12" s="31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q12" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="R12" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="37" t="str">
+        <v>133</v>
+      </c>
+      <c r="R12" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T12" s="37" t="str">
+      <c r="T12" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U12" s="37" t="str">
+      <c r="U12" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V12" s="37" t="str">
+      <c r="V12" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W12" s="68" t="str">
+      <c r="W12" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-12</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y12" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z12" s="36" t="s">
-        <v>158</v>
+        <v>116</v>
+      </c>
+      <c r="Z12" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA12" s="31" t="str">
         <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
         <v>Engine that converts fuel into mechanical energy through external combustion</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="33">
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="59">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="35" t="str">
@@ -3406,80 +3457,80 @@
         <v>Máquina.de.Combustão.Interna</v>
       </c>
       <c r="P13" s="31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="R13" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="37" t="str">
+        <v>134</v>
+      </c>
+      <c r="R13" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T13" s="37" t="str">
+      <c r="T13" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U13" s="37" t="str">
+      <c r="U13" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Maquinária</v>
       </c>
-      <c r="V13" s="37" t="str">
+      <c r="V13" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W13" s="68" t="str">
+      <c r="W13" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-13</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z13" s="36" t="s">
-        <v>158</v>
+        <v>115</v>
+      </c>
+      <c r="Z13" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA13" s="31" t="str">
         <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
         <v>Engine that converts fuel into mechanical energy through internal combustion</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="33">
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="59">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F14" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="56" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="35" t="str">
@@ -3499,80 +3550,80 @@
         <v>Elevador.Hidráulico</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="Q14" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="R14" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="37" t="str">
+        <v>167</v>
+      </c>
+      <c r="R14" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="31" t="str">
         <f t="shared" ref="S14:S19" si="25">SUBSTITUTE(C14, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="T14" s="37" t="str">
+      <c r="T14" s="31" t="str">
         <f t="shared" ref="T14:T19" si="26">SUBSTITUTE(D14, "_", " ")</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U14" s="37" t="str">
+      <c r="U14" s="31" t="str">
         <f t="shared" ref="U14:U19" si="27">SUBSTITUTE(E14, "_", " ")</f>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V14" s="37" t="str">
+      <c r="V14" s="31" t="str">
         <f t="shared" ref="V14:V19" si="28">SUBSTITUTE(C14, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="W14" s="68" t="str">
+      <c r="W14" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-14</v>
       </c>
       <c r="X14" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y14" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z14" s="36" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="Z14" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="AA14" s="31" t="str">
         <f t="shared" ref="AA14:AA16" si="29">_xlfn.TRANSLATE(P14,"pt","en")</f>
         <v>Elevator to a few floors without carrying heavy loads</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="33">
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="59">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="39" t="s">
+      <c r="G15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="35" t="str">
@@ -3592,80 +3643,80 @@
         <v>Elevador.MR</v>
       </c>
       <c r="P15" s="31" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="Q15" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="R15" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="37" t="str">
+        <v>169</v>
+      </c>
+      <c r="R15" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="31" t="str">
         <f t="shared" si="25"/>
         <v>Motricidade</v>
       </c>
-      <c r="T15" s="37" t="str">
+      <c r="T15" s="31" t="str">
         <f t="shared" si="26"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U15" s="37" t="str">
+      <c r="U15" s="31" t="str">
         <f t="shared" si="27"/>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V15" s="37" t="str">
+      <c r="V15" s="31" t="str">
         <f t="shared" si="28"/>
         <v>Motricidade</v>
       </c>
-      <c r="W15" s="68" t="str">
+      <c r="W15" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-15</v>
       </c>
       <c r="X15" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y15" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z15" s="36" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="Z15" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="AA15" s="31" t="str">
         <f t="shared" si="29"/>
         <v>Traction Elevator with Machine Room</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="33">
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="59">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="35" t="str">
@@ -3685,80 +3736,80 @@
         <v>Elevador.MRL</v>
       </c>
       <c r="P16" s="31" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="Q16" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="R16" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="37" t="str">
+        <v>168</v>
+      </c>
+      <c r="R16" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="31" t="str">
         <f t="shared" si="25"/>
         <v>Motricidade</v>
       </c>
-      <c r="T16" s="37" t="str">
+      <c r="T16" s="31" t="str">
         <f t="shared" si="26"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U16" s="37" t="str">
+      <c r="U16" s="31" t="str">
         <f t="shared" si="27"/>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V16" s="37" t="str">
+      <c r="V16" s="31" t="str">
         <f t="shared" si="28"/>
         <v>Motricidade</v>
       </c>
-      <c r="W16" s="68" t="str">
+      <c r="W16" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-16</v>
       </c>
       <c r="X16" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z16" s="36" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="Z16" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="AA16" s="31" t="str">
         <f t="shared" si="29"/>
         <v>Elevator with hoisting pulley without machine room</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="33">
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="59">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F17" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="G17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="35" t="str">
@@ -3778,80 +3829,80 @@
         <v>Plataforma</v>
       </c>
       <c r="P17" s="31" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Q17" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="R17" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="37" t="str">
+        <v>164</v>
+      </c>
+      <c r="R17" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="31" t="str">
         <f t="shared" ref="S17:S18" si="32">SUBSTITUTE(C17, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="T17" s="37" t="str">
+      <c r="T17" s="31" t="str">
         <f t="shared" ref="T17:T18" si="33">SUBSTITUTE(D17, "_", " ")</f>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U17" s="37" t="str">
+      <c r="U17" s="31" t="str">
         <f t="shared" ref="U17:U18" si="34">SUBSTITUTE(E17, "_", " ")</f>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V17" s="37" t="str">
+      <c r="V17" s="31" t="str">
         <f t="shared" ref="V17:V18" si="35">SUBSTITUTE(C17, "_", " ")</f>
         <v>Motricidade</v>
       </c>
-      <c r="W17" s="68" t="str">
+      <c r="W17" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-17</v>
       </c>
       <c r="X17" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y17" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z17" s="36" t="s">
-        <v>183</v>
+        <v>175</v>
+      </c>
+      <c r="Z17" s="31" t="s">
+        <v>178</v>
       </c>
       <c r="AA17" s="31" t="str">
         <f>_xlfn.TRANSLATE(P17,"pt","en")</f>
         <v>Lifting Platform</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="33">
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="59">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="35" t="str">
@@ -3871,80 +3922,80 @@
         <v>Plataforma.Articulada</v>
       </c>
       <c r="P18" s="31" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Q18" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="R18" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="37" t="str">
+        <v>171</v>
+      </c>
+      <c r="R18" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="31" t="str">
         <f t="shared" si="32"/>
         <v>Motricidade</v>
       </c>
-      <c r="T18" s="37" t="str">
+      <c r="T18" s="31" t="str">
         <f t="shared" si="33"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U18" s="37" t="str">
+      <c r="U18" s="31" t="str">
         <f t="shared" si="34"/>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V18" s="37" t="str">
+      <c r="V18" s="31" t="str">
         <f t="shared" si="35"/>
         <v>Motricidade</v>
       </c>
-      <c r="W18" s="68" t="str">
+      <c r="W18" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-18</v>
       </c>
       <c r="X18" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y18" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z18" s="36" t="s">
-        <v>183</v>
+        <v>175</v>
+      </c>
+      <c r="Z18" s="31" t="s">
+        <v>178</v>
       </c>
       <c r="AA18" s="31" t="str">
         <f>_xlfn.TRANSLATE(P18,"pt","en")</f>
         <v>Articulated lifting platform</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="33">
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="59">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="35" t="str">
@@ -3964,80 +4015,80 @@
         <v>Plataforma.Cesto</v>
       </c>
       <c r="P19" s="31" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="R19" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="37" t="str">
+        <v>170</v>
+      </c>
+      <c r="R19" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="31" t="str">
         <f t="shared" si="25"/>
         <v>Motricidade</v>
       </c>
-      <c r="T19" s="37" t="str">
+      <c r="T19" s="31" t="str">
         <f t="shared" si="26"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U19" s="37" t="str">
+      <c r="U19" s="31" t="str">
         <f t="shared" si="27"/>
         <v>Maquinária.de.Elevação</v>
       </c>
-      <c r="V19" s="37" t="str">
+      <c r="V19" s="31" t="str">
         <f t="shared" si="28"/>
         <v>Motricidade</v>
       </c>
-      <c r="W19" s="68" t="str">
+      <c r="W19" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-19</v>
       </c>
       <c r="X19" s="31" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y19" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z19" s="36" t="s">
-        <v>183</v>
+        <v>175</v>
+      </c>
+      <c r="Z19" s="31" t="s">
+        <v>178</v>
       </c>
       <c r="AA19" s="31" t="str">
         <f>_xlfn.TRANSLATE(P19,"pt","en")</f>
         <v>Basket lifting platform</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="33">
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="59">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="60" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="35" t="str">
@@ -4057,42 +4108,42 @@
         <v>Acessório.Maquinária</v>
       </c>
       <c r="P20" s="31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="R20" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="37" t="str">
+        <v>135</v>
+      </c>
+      <c r="R20" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="31" t="str">
         <f t="shared" si="8"/>
         <v>Motricidade</v>
       </c>
-      <c r="T20" s="37" t="str">
+      <c r="T20" s="31" t="str">
         <f t="shared" si="9"/>
         <v>Elementos.de.Força.Motriz</v>
       </c>
-      <c r="U20" s="37" t="str">
+      <c r="U20" s="31" t="str">
         <f t="shared" si="10"/>
         <v>Acessórios.Maquinária</v>
       </c>
-      <c r="V20" s="37" t="str">
+      <c r="V20" s="31" t="str">
         <f t="shared" si="17"/>
         <v>Motricidade</v>
       </c>
-      <c r="W20" s="68" t="str">
+      <c r="W20" s="61" t="str">
         <f t="shared" si="11"/>
         <v>Key-MOT-20</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Y20" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z20" s="36" t="s">
-        <v>158</v>
+        <v>104</v>
+      </c>
+      <c r="Z20" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="AA20" s="31" t="str">
         <f t="shared" ref="AA20" si="40">_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -4104,59 +4155,64 @@
     <sortCondition ref="F7:F745"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="29" priority="223" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="229" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="28" priority="1659"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F10">
-    <cfRule type="duplicateValues" dxfId="23" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F13">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F19">
-    <cfRule type="duplicateValues" dxfId="16" priority="2094"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="15" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="2012"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2018"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2019"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2020"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X7:X20">
-    <cfRule type="containsText" dxfId="8" priority="50" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="14" priority="56" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA19">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA7:AA19">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B20">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4168,15 +4224,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4241,7 +4297,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4306,7 +4362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -4373,7 +4429,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4389,617 +4445,616 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.61328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.15234375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.28515625" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" style="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="59" t="s">
-        <v>77</v>
-      </c>
       <c r="I1" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="54" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="60" t="s">
+      <c r="L2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="60" t="s">
+      <c r="P2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>3</v>
       </c>
-      <c r="B3" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="40" t="s">
+      <c r="B3" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P3" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R3" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H3" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J3" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L3" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P3" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R3" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S3" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S3" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>4</v>
       </c>
-      <c r="B4" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="40" t="s">
+      <c r="B4" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P4" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R4" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L4" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P4" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R4" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S4" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S4" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>5</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="B5" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P5" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R5" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L5" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P5" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R5" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S5" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S5" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>6</v>
       </c>
-      <c r="B6" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="40" t="s">
+      <c r="B6" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R6" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J6" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L6" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P6" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R6" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S6" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S6" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>7</v>
       </c>
-      <c r="B7" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="40" t="s">
+      <c r="B7" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P7" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R7" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H7" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J7" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L7" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P7" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R7" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S7" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S7" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>8</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="40" t="s">
+      <c r="H8" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P8" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R8" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H8" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L8" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="60" t="s">
+      <c r="S8" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
+        <v>9</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J9" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="O8" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P8" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R8" s="60" t="s">
+      <c r="K9" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="S8" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21">
-        <v>9</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="40" t="s">
+      <c r="O9" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P9" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R9" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L9" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P9" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R9" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S9" s="67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="S9" s="58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="40" t="s">
+      <c r="B10" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="P10" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="R10" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H10" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="J10" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="O10" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P10" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q10" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="R10" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="S10" s="67" t="s">
-        <v>159</v>
+      <c r="S10" s="58" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -5012,38 +5067,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.921875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.23046875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32">
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="D1" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="29" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -5072,22 +5127,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/MOTO/Ontologia_Motriz.xlsx
+++ b/Versão5/MOTO/Ontologia_Motriz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6756EAE9-437E-4919-B054-6E274D6B9FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4796EFEF-9C28-4653-A919-690970D399BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="198">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -641,9 +641,6 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -663,6 +660,12 @@
   </si>
   <si>
     <t>CTI_Projeto_A</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>De.Motricidade</t>
   </si>
 </sst>
 </file>
@@ -1208,63 +1211,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -1994,14 +1941,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="47.15234375" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2012,7 +1959,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2023,7 +1970,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2034,7 +1981,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2045,7 +1992,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2057,7 +2004,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2069,7 +2016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2080,7 +2027,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="40" t="s">
         <v>54</v>
       </c>
@@ -2091,7 +2038,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2102,7 +2049,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2113,7 +2060,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2124,7 +2071,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2135,7 +2082,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2146,7 +2093,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2157,7 +2104,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2168,7 +2115,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2179,7 +2126,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2190,19 +2137,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46216.399269444446</v>
+        <v>46243.535029513892</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2213,7 +2160,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2224,7 +2171,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2235,7 +2182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2246,7 +2193,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2257,7 +2204,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="41" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>90</v>
       </c>
@@ -2278,35 +2225,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.15234375" style="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" style="62" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="66" customWidth="1"/>
     <col min="7" max="11" width="8" style="62" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="62" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.85546875" style="62" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" style="62" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.5703125" style="62" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5703125" style="67" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="62"/>
+    <col min="12" max="12" width="7.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.15234375" style="62" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" style="62" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.84375" style="62" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.15234375" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.3046875" style="62" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.84375" style="62" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.53515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.53515625" style="67" customWidth="1"/>
+    <col min="26" max="26" width="10.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>95</v>
       </c>
@@ -2389,12 +2336,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="59">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>180</v>
@@ -2403,7 +2350,7 @@
         <v>83</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F2" s="56" t="s">
         <v>82</v>
@@ -2474,19 +2421,19 @@
         <v>9</v>
       </c>
       <c r="Z2" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AA2" s="31" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="59">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>180</v>
@@ -2495,7 +2442,7 @@
         <v>83</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F3" s="56" t="s">
         <v>181</v>
@@ -2573,12 +2520,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="59">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>180</v>
@@ -2587,7 +2534,7 @@
         <v>83</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F4" s="56" t="s">
         <v>183</v>
@@ -2665,12 +2612,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="59">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>180</v>
@@ -2679,7 +2626,7 @@
         <v>83</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F5" s="56" t="s">
         <v>185</v>
@@ -2757,12 +2704,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="59">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>180</v>
@@ -2771,7 +2718,7 @@
         <v>83</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F6" s="56" t="s">
         <v>187</v>
@@ -2849,15 +2796,15 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="59">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>151</v>
@@ -2885,7 +2832,7 @@
       </c>
       <c r="L7" s="35" t="str">
         <f t="shared" ref="L7:L9" si="5">CONCATENATE("", C7)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M7" s="35" t="str">
         <f t="shared" ref="M7:M9" si="6">CONCATENATE("", D7)</f>
@@ -2910,7 +2857,7 @@
       </c>
       <c r="S7" s="31" t="str">
         <f t="shared" ref="S7:S20" si="8">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T7" s="31" t="str">
         <f t="shared" ref="T7:T20" si="9">SUBSTITUTE(D7, "_", " ")</f>
@@ -2941,15 +2888,15 @@
         <v>Combustion engine</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="59">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>151</v>
@@ -2977,7 +2924,7 @@
       </c>
       <c r="L8" s="35" t="str">
         <f t="shared" ref="L8" si="13">CONCATENATE("", C8)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M8" s="35" t="str">
         <f t="shared" ref="M8" si="14">CONCATENATE("", D8)</f>
@@ -3002,7 +2949,7 @@
       </c>
       <c r="S8" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T8" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3014,7 +2961,7 @@
       </c>
       <c r="V8" s="31" t="str">
         <f t="shared" ref="V8:V20" si="17">SUBSTITUTE(C8, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W8" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3034,15 +2981,15 @@
         <v>Coupling motor</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="59">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>151</v>
@@ -3070,7 +3017,7 @@
       </c>
       <c r="L9" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M9" s="35" t="str">
         <f t="shared" si="6"/>
@@ -3095,7 +3042,7 @@
       </c>
       <c r="S9" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T9" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3107,7 +3054,7 @@
       </c>
       <c r="V9" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W9" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3127,15 +3074,15 @@
         <v>Belt drive motor</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="59">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>151</v>
@@ -3163,7 +3110,7 @@
       </c>
       <c r="L10" s="35" t="str">
         <f t="shared" ref="L10" si="19">CONCATENATE("", C10)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M10" s="35" t="str">
         <f t="shared" ref="M10" si="20">CONCATENATE("", D10)</f>
@@ -3188,7 +3135,7 @@
       </c>
       <c r="S10" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T10" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3200,7 +3147,7 @@
       </c>
       <c r="V10" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W10" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3220,15 +3167,15 @@
         <v>Direct drive motor</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="59">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>151</v>
@@ -3256,7 +3203,7 @@
       </c>
       <c r="L11" s="35" t="str">
         <f t="shared" ref="L11:M18" si="23">CONCATENATE("", C11)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M11" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3281,7 +3228,7 @@
       </c>
       <c r="S11" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T11" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3293,7 +3240,7 @@
       </c>
       <c r="V11" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W11" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3313,15 +3260,15 @@
         <v>Engine that converts fuel into mechanical energy through combustion</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="59">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>151</v>
@@ -3349,7 +3296,7 @@
       </c>
       <c r="L12" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M12" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3374,7 +3321,7 @@
       </c>
       <c r="S12" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T12" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3386,7 +3333,7 @@
       </c>
       <c r="V12" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W12" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3406,15 +3353,15 @@
         <v>Engine that converts fuel into mechanical energy through external combustion</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="59">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>151</v>
@@ -3442,7 +3389,7 @@
       </c>
       <c r="L13" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M13" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3467,7 +3414,7 @@
       </c>
       <c r="S13" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T13" s="31" t="str">
         <f t="shared" si="9"/>
@@ -3479,7 +3426,7 @@
       </c>
       <c r="V13" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W13" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3499,15 +3446,15 @@
         <v>Engine that converts fuel into mechanical energy through internal combustion</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="59">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>151</v>
@@ -3535,7 +3482,7 @@
       </c>
       <c r="L14" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M14" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3560,7 +3507,7 @@
       </c>
       <c r="S14" s="31" t="str">
         <f t="shared" ref="S14:S19" si="25">SUBSTITUTE(C14, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T14" s="31" t="str">
         <f t="shared" ref="T14:T19" si="26">SUBSTITUTE(D14, "_", " ")</f>
@@ -3572,7 +3519,7 @@
       </c>
       <c r="V14" s="31" t="str">
         <f t="shared" ref="V14:V19" si="28">SUBSTITUTE(C14, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W14" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3592,15 +3539,15 @@
         <v>Elevator to a few floors without carrying heavy loads</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="59">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -3628,7 +3575,7 @@
       </c>
       <c r="L15" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M15" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3653,7 +3600,7 @@
       </c>
       <c r="S15" s="31" t="str">
         <f t="shared" si="25"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T15" s="31" t="str">
         <f t="shared" si="26"/>
@@ -3665,7 +3612,7 @@
       </c>
       <c r="V15" s="31" t="str">
         <f t="shared" si="28"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W15" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3685,15 +3632,15 @@
         <v>Traction Elevator with Machine Room</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="59">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>151</v>
@@ -3721,7 +3668,7 @@
       </c>
       <c r="L16" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M16" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3746,7 +3693,7 @@
       </c>
       <c r="S16" s="31" t="str">
         <f t="shared" si="25"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T16" s="31" t="str">
         <f t="shared" si="26"/>
@@ -3758,7 +3705,7 @@
       </c>
       <c r="V16" s="31" t="str">
         <f t="shared" si="28"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W16" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3778,15 +3725,15 @@
         <v>Elevator with hoisting pulley without machine room</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="59">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>151</v>
@@ -3814,7 +3761,7 @@
       </c>
       <c r="L17" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M17" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3839,7 +3786,7 @@
       </c>
       <c r="S17" s="31" t="str">
         <f t="shared" ref="S17:S18" si="32">SUBSTITUTE(C17, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T17" s="31" t="str">
         <f t="shared" ref="T17:T18" si="33">SUBSTITUTE(D17, "_", " ")</f>
@@ -3851,7 +3798,7 @@
       </c>
       <c r="V17" s="31" t="str">
         <f t="shared" ref="V17:V18" si="35">SUBSTITUTE(C17, "_", " ")</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W17" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3871,15 +3818,15 @@
         <v>Lifting Platform</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="59">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>151</v>
@@ -3907,7 +3854,7 @@
       </c>
       <c r="L18" s="35" t="str">
         <f t="shared" si="23"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M18" s="35" t="str">
         <f t="shared" si="23"/>
@@ -3932,7 +3879,7 @@
       </c>
       <c r="S18" s="31" t="str">
         <f t="shared" si="32"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T18" s="31" t="str">
         <f t="shared" si="33"/>
@@ -3944,7 +3891,7 @@
       </c>
       <c r="V18" s="31" t="str">
         <f t="shared" si="35"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W18" s="61" t="str">
         <f t="shared" si="11"/>
@@ -3964,15 +3911,15 @@
         <v>Articulated lifting platform</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="59">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>151</v>
@@ -4000,7 +3947,7 @@
       </c>
       <c r="L19" s="35" t="str">
         <f t="shared" ref="L19" si="36">CONCATENATE("", C19)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M19" s="35" t="str">
         <f t="shared" ref="M19" si="37">CONCATENATE("", D19)</f>
@@ -4025,7 +3972,7 @@
       </c>
       <c r="S19" s="31" t="str">
         <f t="shared" si="25"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T19" s="31" t="str">
         <f t="shared" si="26"/>
@@ -4037,7 +3984,7 @@
       </c>
       <c r="V19" s="31" t="str">
         <f t="shared" si="28"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W19" s="61" t="str">
         <f t="shared" si="11"/>
@@ -4057,15 +4004,15 @@
         <v>Basket lifting platform</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="59">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>151</v>
@@ -4093,7 +4040,7 @@
       </c>
       <c r="L20" s="35" t="str">
         <f t="shared" ref="L20:M20" si="38">CONCATENATE("", C20)</f>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="M20" s="35" t="str">
         <f t="shared" si="38"/>
@@ -4118,7 +4065,7 @@
       </c>
       <c r="S20" s="31" t="str">
         <f t="shared" si="8"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="T20" s="31" t="str">
         <f t="shared" si="9"/>
@@ -4130,7 +4077,7 @@
       </c>
       <c r="V20" s="31" t="str">
         <f t="shared" si="17"/>
-        <v>Motricidade</v>
+        <v>De.Motricidade</v>
       </c>
       <c r="W20" s="61" t="str">
         <f t="shared" si="11"/>
@@ -4155,64 +4102,59 @@
     <sortCondition ref="F7:F745"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:B20">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="35" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="229" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="34" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1665"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F10">
-    <cfRule type="duplicateValues" dxfId="29" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F13">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F19">
-    <cfRule type="duplicateValues" dxfId="22" priority="2100"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="21" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="20" priority="2008"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="2018"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2024"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2025"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2026"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2068"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X7:X20">
-    <cfRule type="containsText" dxfId="14" priority="56" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="8" priority="56" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B20">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA19">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4224,15 +4166,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4297,7 +4239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4362,7 +4304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -4429,7 +4371,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4445,29 +4387,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.28515625" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="34.3046875" customWidth="1"/>
+    <col min="8" max="8" width="6.69140625" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53515625" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" customWidth="1"/>
+    <col min="15" max="15" width="13.84375" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -4526,12 +4468,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C2" s="55" t="s">
         <v>82</v>
@@ -4585,7 +4527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -4599,7 +4541,7 @@
         <v>102</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>77</v>
@@ -4608,10 +4550,10 @@
         <v>145</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J3" s="52" t="s">
         <v>103</v>
@@ -4629,13 +4571,13 @@
         <v>101</v>
       </c>
       <c r="O3" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P3" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R3" s="52" t="s">
         <v>99</v>
@@ -4644,7 +4586,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -4658,7 +4600,7 @@
         <v>102</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>77</v>
@@ -4667,10 +4609,10 @@
         <v>145</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J4" s="52" t="s">
         <v>103</v>
@@ -4688,13 +4630,13 @@
         <v>101</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P4" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R4" s="52" t="s">
         <v>99</v>
@@ -4703,7 +4645,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -4717,7 +4659,7 @@
         <v>102</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>77</v>
@@ -4726,10 +4668,10 @@
         <v>145</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="52" t="s">
         <v>103</v>
@@ -4747,13 +4689,13 @@
         <v>101</v>
       </c>
       <c r="O5" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P5" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R5" s="52" t="s">
         <v>99</v>
@@ -4762,7 +4704,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -4776,7 +4718,7 @@
         <v>102</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>77</v>
@@ -4785,10 +4727,10 @@
         <v>145</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J6" s="52" t="s">
         <v>103</v>
@@ -4806,13 +4748,13 @@
         <v>101</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P6" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R6" s="52" t="s">
         <v>99</v>
@@ -4821,7 +4763,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -4835,7 +4777,7 @@
         <v>102</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>77</v>
@@ -4844,10 +4786,10 @@
         <v>145</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J7" s="52" t="s">
         <v>103</v>
@@ -4865,13 +4807,13 @@
         <v>101</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P7" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R7" s="52" t="s">
         <v>99</v>
@@ -4880,7 +4822,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -4894,7 +4836,7 @@
         <v>102</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>77</v>
@@ -4903,10 +4845,10 @@
         <v>145</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J8" s="52" t="s">
         <v>103</v>
@@ -4924,13 +4866,13 @@
         <v>101</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P8" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R8" s="52" t="s">
         <v>99</v>
@@ -4939,7 +4881,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -4953,7 +4895,7 @@
         <v>102</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>77</v>
@@ -4962,10 +4904,10 @@
         <v>145</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J9" s="52" t="s">
         <v>103</v>
@@ -4983,13 +4925,13 @@
         <v>101</v>
       </c>
       <c r="O9" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P9" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q9" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R9" s="52" t="s">
         <v>99</v>
@@ -4998,7 +4940,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -5012,7 +4954,7 @@
         <v>102</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>77</v>
@@ -5021,10 +4963,10 @@
         <v>145</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J10" s="52" t="s">
         <v>103</v>
@@ -5042,13 +4984,13 @@
         <v>101</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P10" s="52" t="s">
         <v>100</v>
       </c>
       <c r="Q10" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R10" s="52" t="s">
         <v>99</v>
@@ -5067,15 +5009,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="32">
         <v>0</v>
       </c>
@@ -5098,7 +5040,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -5127,22 +5069,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
